--- a/Exce_ Basic_Assignments.xlsx
+++ b/Exce_ Basic_Assignments.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Shamshad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92F68089-36A4-47B1-A1CA-3C11F328622F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA570B6B-38AD-4B29-9E73-C62ACF08AE82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Student Report" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="148">
   <si>
     <t>S.No.</t>
   </si>
@@ -337,11 +339,68 @@
     <t>Static number</t>
   </si>
   <si>
-    <t>Changes when copied to another cell</t>
+    <t>### 🔸 **Section D: Excel Functions**</t>
+  </si>
+  <si>
+    <t>8. **Functions:**</t>
+  </si>
+  <si>
+    <t>* Use the following functions in column J:</t>
+  </si>
+  <si>
+    <t>Marks</t>
+  </si>
+  <si>
+    <t>* In I1\:I5, enter marks for 5 students.</t>
+  </si>
+  <si>
+    <t>Student</t>
+  </si>
+  <si>
+    <t>AVG</t>
+  </si>
+  <si>
+    <t>SUM</t>
+  </si>
+  <si>
+    <t>MAX</t>
+  </si>
+  <si>
+    <t>MIN</t>
+  </si>
+  <si>
+    <t>Stu1</t>
+  </si>
+  <si>
+    <t>Stu2</t>
+  </si>
+  <si>
+    <t>Stu3</t>
+  </si>
+  <si>
+    <t>Stu4</t>
+  </si>
+  <si>
+    <t>Stu5</t>
+  </si>
+  <si>
+    <t>Func_Result</t>
+  </si>
+  <si>
+    <t>Function</t>
+  </si>
+  <si>
+    <t>Use IF Condition</t>
+  </si>
+  <si>
+    <t>Col</t>
+  </si>
+  <si>
+    <t>(N3+N4) Changes when copied to another cell</t>
   </si>
   <si>
     <r>
-      <t>$H$1</t>
+      <t>$N$3+$N$4</t>
     </r>
     <r>
       <rPr>
@@ -351,36 +410,209 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> is fixed, </t>
+      <t xml:space="preserve"> is fixed, so it won’t change even if copied to other cells.</t>
+    </r>
+  </si>
+  <si>
+    <t>Elements</t>
+  </si>
+  <si>
+    <t>Rows</t>
+  </si>
+  <si>
+    <t>Columns</t>
+  </si>
+  <si>
+    <t>5. **Elements of Excel Sheet:**</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> * Identify and label (in comments or a side column):</t>
+  </si>
+  <si>
+    <t>* **Rows**, **Columns**, **Cell Address**, **Formula Bar**, and **Sheet Tabs**</t>
+  </si>
+  <si>
+    <t>Cell Address</t>
+  </si>
+  <si>
+    <t>Formula Bar</t>
+  </si>
+  <si>
+    <t>Sheet Tabs</t>
+  </si>
+  <si>
+    <t>Located above the worksheet; used to view, enter, or edit formulas/data.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Horizontal lines in the sheet / set of cells,  numbered </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1, 2, 3, …</t>
     </r>
     <r>
       <rPr>
         <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
-      <t>H2</t>
+      <t xml:space="preserve"> on the left side/left margin.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Vertical lines in the sheet / set of cells, labeled </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A, B, C, …, Z, AA…</t>
     </r>
     <r>
       <rPr>
         <sz val="12"/>
-        <color theme="1"/>
+        <color rgb="FF0070C0"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> changes when copied</t>
+      <t xml:space="preserve"> at the top.</t>
     </r>
   </si>
   <si>
-    <t>Sum</t>
+    <r>
+      <t xml:space="preserve">The unique reference of a cell, shown as </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Column Letter + Row Number</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (e.g., </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>B3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Tabs at the bottom of the workbook used to navigate between different sheets (e.g., </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Sheet1, Sheet2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <t>### 🔸 **Bonus Task (Optional): Create a mini-report**</t>
+  </si>
+  <si>
+    <t>* Format a small **table** with borders, headers (bold), and fill colors.</t>
+  </si>
+  <si>
+    <t>* Include at least **2 formulas** and **1 cell reference type**.</t>
+  </si>
+  <si>
+    <t>* Add a **sheet name** (e.g., "Student Report") and save the file.</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Average_Marks</t>
+  </si>
+  <si>
+    <t>Total_Marks</t>
+  </si>
+  <si>
+    <t>Sindhu</t>
+  </si>
+  <si>
+    <t>Gayathri</t>
+  </si>
+  <si>
+    <t>Class_Avg</t>
+  </si>
+  <si>
+    <t>Relative_Ref</t>
+  </si>
+  <si>
+    <t>Ref_Type</t>
+  </si>
+  <si>
+    <t>Absolute_Ref</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="31">
+  <fonts count="46">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -608,8 +840,119 @@
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
     </font>
+    <font>
+      <i/>
+      <u/>
+      <sz val="16"/>
+      <color theme="5"/>
+      <name val="Comic Sans MS"/>
+      <family val="4"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="14"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="7" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="5"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="8" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF66FF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -652,6 +995,42 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="12">
     <border>
@@ -815,10 +1194,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -868,39 +1248,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -939,9 +1286,6 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -957,98 +1301,229 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="135"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="135"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="43" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1353,70 +1828,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="28.8" customHeight="1">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="89" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="K1" s="30" t="s">
+      <c r="B1" s="89"/>
+      <c r="C1" s="89"/>
+      <c r="D1" s="89"/>
+      <c r="E1" s="89"/>
+      <c r="F1" s="89"/>
+      <c r="G1" s="89"/>
+      <c r="H1" s="89"/>
+      <c r="K1" s="88" t="s">
         <v>52</v>
       </c>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="R1" s="79" t="s">
+      <c r="L1" s="88"/>
+      <c r="M1" s="88"/>
+      <c r="R1" s="91" t="s">
         <v>67</v>
       </c>
-      <c r="S1" s="79"/>
-      <c r="T1" s="79"/>
+      <c r="S1" s="91"/>
+      <c r="T1" s="91"/>
     </row>
     <row r="2" spans="1:20" ht="31.95" customHeight="1">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="85" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="K2" s="64" t="s">
+      <c r="B2" s="85"/>
+      <c r="C2" s="85"/>
+      <c r="D2" s="85"/>
+      <c r="E2" s="85"/>
+      <c r="F2" s="85"/>
+      <c r="G2" s="85"/>
+      <c r="H2" s="85"/>
+      <c r="K2" s="90" t="s">
         <v>53</v>
       </c>
-      <c r="L2" s="64"/>
-      <c r="M2" s="64"/>
-      <c r="R2" s="78" t="s">
+      <c r="L2" s="90"/>
+      <c r="M2" s="90"/>
+      <c r="R2" s="92" t="s">
         <v>68</v>
       </c>
-      <c r="S2" s="78"/>
-      <c r="T2" s="78"/>
+      <c r="S2" s="92"/>
+      <c r="T2" s="92"/>
     </row>
     <row r="3" spans="1:20" ht="31.95" customHeight="1">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="86" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="K3" s="27" t="s">
+      <c r="B3" s="86"/>
+      <c r="C3" s="86"/>
+      <c r="D3" s="86"/>
+      <c r="E3" s="86"/>
+      <c r="F3" s="86"/>
+      <c r="G3" s="86"/>
+      <c r="H3" s="86"/>
+      <c r="K3" s="85" t="s">
         <v>54</v>
       </c>
-      <c r="L3" s="27"/>
-      <c r="M3" s="27"/>
-      <c r="R3" s="80" t="s">
+      <c r="L3" s="85"/>
+      <c r="M3" s="85"/>
+      <c r="R3" s="64" t="s">
         <v>69</v>
       </c>
-      <c r="S3" s="80"/>
-      <c r="T3" s="80"/>
+      <c r="S3" s="64"/>
+      <c r="T3" s="64"/>
     </row>
     <row r="4" spans="1:20" s="25" customFormat="1" ht="30" customHeight="1">
       <c r="A4" s="24" t="s">
@@ -1443,264 +1918,261 @@
       <c r="H4" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="61"/>
-      <c r="K4" s="63" t="s">
+      <c r="J4" s="49"/>
+      <c r="K4" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="L4" s="63" t="s">
+      <c r="L4" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="M4" s="63" t="s">
+      <c r="M4" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="R4" s="84" t="s">
+      <c r="R4" s="68" t="s">
         <v>36</v>
       </c>
-      <c r="S4" s="84" t="s">
+      <c r="S4" s="68" t="s">
         <v>59</v>
       </c>
-      <c r="T4" s="84" t="s">
+      <c r="T4" s="68" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:20" s="40" customFormat="1" ht="49.95" customHeight="1">
-      <c r="A5" s="38">
+    <row r="5" spans="1:20" s="29" customFormat="1" ht="49.95" customHeight="1">
+      <c r="A5" s="27">
         <v>1</v>
       </c>
-      <c r="B5" s="46" t="s">
+      <c r="B5" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="44" t="s">
+      <c r="C5" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="44">
+      <c r="D5" s="33">
         <v>10</v>
       </c>
-      <c r="E5" s="44" t="s">
+      <c r="E5" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="44" t="s">
+      <c r="F5" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="44" t="s">
+      <c r="G5" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="44" t="s">
+      <c r="H5" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="I5" s="39"/>
-      <c r="J5" s="39"/>
-      <c r="K5" s="65" t="s">
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="L5" s="65" t="s">
+      <c r="L5" s="52" t="s">
         <v>48</v>
       </c>
-      <c r="M5" s="66" t="s">
+      <c r="M5" s="53" t="s">
         <v>49</v>
       </c>
-      <c r="N5" s="39"/>
-      <c r="O5" s="39"/>
-      <c r="R5" s="85" t="s">
+      <c r="N5" s="28"/>
+      <c r="O5" s="28"/>
+      <c r="R5" s="69" t="s">
         <v>56</v>
       </c>
-      <c r="S5" s="82" t="s">
+      <c r="S5" s="66" t="s">
         <v>61</v>
       </c>
-      <c r="T5" s="86" t="s">
+      <c r="T5" s="70" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:20" s="42" customFormat="1" ht="100.05" customHeight="1">
-      <c r="A6" s="41">
+    <row r="6" spans="1:20" s="31" customFormat="1" ht="100.05" customHeight="1">
+      <c r="A6" s="30">
         <v>2</v>
       </c>
-      <c r="B6" s="45" t="s">
+      <c r="B6" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="45" t="s">
+      <c r="C6" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="45">
+      <c r="D6" s="34">
         <v>11</v>
       </c>
-      <c r="E6" s="45" t="s">
+      <c r="E6" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="45" t="s">
+      <c r="F6" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="G6" s="45" t="s">
+      <c r="G6" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="45" t="s">
+      <c r="H6" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="43"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="67" t="s">
+      <c r="I6" s="32"/>
+      <c r="J6" s="50"/>
+      <c r="K6" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="L6" s="67" t="s">
+      <c r="L6" s="54" t="s">
         <v>42</v>
       </c>
-      <c r="M6" s="68" t="s">
+      <c r="M6" s="55" t="s">
         <v>50</v>
       </c>
-      <c r="N6" s="43"/>
-      <c r="O6" s="43"/>
-      <c r="R6" s="85" t="s">
+      <c r="N6" s="32"/>
+      <c r="O6" s="32"/>
+      <c r="R6" s="69" t="s">
         <v>57</v>
       </c>
-      <c r="S6" s="83" t="s">
+      <c r="S6" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="T6" s="86" t="s">
+      <c r="T6" s="70" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="1:20" s="51" customFormat="1" ht="49.95" customHeight="1">
-      <c r="A7" s="49">
+    <row r="7" spans="1:20" s="40" customFormat="1" ht="49.95" customHeight="1">
+      <c r="A7" s="38">
         <v>3</v>
       </c>
-      <c r="B7" s="50" t="s">
+      <c r="B7" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="47" t="s">
+      <c r="C7" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="47">
+      <c r="D7" s="36">
         <v>12</v>
       </c>
-      <c r="E7" s="47" t="s">
+      <c r="E7" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="47" t="s">
+      <c r="F7" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="47" t="s">
+      <c r="G7" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="H7" s="47" t="s">
+      <c r="H7" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="I7" s="48"/>
-      <c r="J7" s="48"/>
-      <c r="K7" s="69" t="s">
+      <c r="I7" s="37"/>
+      <c r="J7" s="37"/>
+      <c r="K7" s="56" t="s">
         <v>45</v>
       </c>
-      <c r="L7" s="69" t="s">
+      <c r="L7" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="M7" s="70" t="s">
+      <c r="M7" s="57" t="s">
         <v>51</v>
       </c>
-      <c r="N7" s="48"/>
-      <c r="O7" s="48"/>
-      <c r="R7" s="87" t="s">
+      <c r="N7" s="37"/>
+      <c r="O7" s="37"/>
+      <c r="R7" s="71" t="s">
         <v>58</v>
       </c>
-      <c r="S7" s="81" t="s">
+      <c r="S7" s="65" t="s">
         <v>63</v>
       </c>
-      <c r="T7" s="86" t="s">
+      <c r="T7" s="70" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="8" spans="1:20" s="54" customFormat="1" ht="17.399999999999999">
-      <c r="A8" s="60">
+    <row r="8" spans="1:20" s="43" customFormat="1" ht="17.399999999999999">
+      <c r="A8" s="48">
         <v>4</v>
       </c>
-      <c r="B8" s="52" t="s">
+      <c r="B8" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="52" t="s">
+      <c r="C8" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="52">
+      <c r="D8" s="41">
         <v>14</v>
       </c>
-      <c r="E8" s="52" t="s">
+      <c r="E8" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="52" t="s">
+      <c r="F8" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="52" t="s">
+      <c r="G8" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="H8" s="52" t="s">
+      <c r="H8" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="I8" s="53"/>
-      <c r="J8" s="53"/>
-      <c r="K8" s="71" t="s">
+      <c r="I8" s="42"/>
+      <c r="J8" s="42"/>
+      <c r="K8" s="58" t="s">
         <v>46</v>
       </c>
-      <c r="L8" s="71" t="s">
+      <c r="L8" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="M8" s="72" t="s">
+      <c r="M8" s="59" t="s">
         <v>35</v>
       </c>
-      <c r="N8" s="53"/>
-      <c r="O8" s="53"/>
-    </row>
-    <row r="9" spans="1:20" s="59" customFormat="1" ht="25.2">
-      <c r="A9" s="55">
+      <c r="N8" s="42"/>
+      <c r="O8" s="42"/>
+    </row>
+    <row r="9" spans="1:20" s="47" customFormat="1" ht="25.2">
+      <c r="A9" s="44">
         <v>5</v>
       </c>
-      <c r="B9" s="56" t="s">
+      <c r="B9" s="75" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="57" t="s">
+      <c r="C9" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="57">
+      <c r="D9" s="45">
         <v>16</v>
       </c>
-      <c r="E9" s="57" t="s">
+      <c r="E9" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="F9" s="57" t="s">
+      <c r="F9" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="G9" s="57" t="s">
+      <c r="G9" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="H9" s="57" t="s">
+      <c r="H9" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="I9" s="58"/>
-      <c r="J9" s="58"/>
-      <c r="K9" s="73" t="s">
+      <c r="I9" s="46"/>
+      <c r="J9" s="46"/>
+      <c r="K9" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="L9" s="73" t="s">
+      <c r="L9" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="M9" s="74" t="s">
+      <c r="M9" s="61" t="s">
         <v>55</v>
       </c>
-      <c r="N9" s="58"/>
-      <c r="O9" s="76"/>
-    </row>
-    <row r="10" spans="1:20">
-      <c r="O10" s="75"/>
+      <c r="N9" s="46"/>
+      <c r="O9" s="62"/>
     </row>
     <row r="19" spans="1:5" ht="21">
-      <c r="A19" s="30"/>
-      <c r="B19" s="30"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
+      <c r="A19" s="88"/>
+      <c r="B19" s="88"/>
+      <c r="C19" s="88"/>
+      <c r="D19" s="88"/>
+      <c r="E19" s="88"/>
     </row>
     <row r="20" spans="1:5" ht="18">
-      <c r="A20" s="29"/>
-      <c r="B20" s="29"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="29"/>
+      <c r="A20" s="87"/>
+      <c r="B20" s="87"/>
+      <c r="C20" s="87"/>
+      <c r="D20" s="87"/>
+      <c r="E20" s="87"/>
     </row>
     <row r="21" spans="1:5" ht="18">
       <c r="A21" s="6"/>
@@ -1752,57 +2224,68 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C144CD9-47B2-4264-8080-0D337456D824}">
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="5" max="5" width="36.21875" customWidth="1"/>
     <col min="8" max="8" width="14.6640625" customWidth="1"/>
     <col min="9" max="9" width="19.6640625" customWidth="1"/>
     <col min="10" max="10" width="42.5546875" customWidth="1"/>
+    <col min="13" max="13" width="11.6640625" customWidth="1"/>
     <col min="14" max="14" width="18.5546875" customWidth="1"/>
-    <col min="15" max="15" width="14.5546875" customWidth="1"/>
-    <col min="16" max="16" width="25.109375" customWidth="1"/>
-    <col min="17" max="17" width="44.44140625" customWidth="1"/>
+    <col min="15" max="15" width="25.109375" customWidth="1"/>
+    <col min="16" max="16" width="69.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="21">
-      <c r="A1" s="32" t="s">
+    <row r="1" spans="1:16" ht="21">
+      <c r="A1" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="34"/>
-      <c r="G1" s="89" t="s">
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="97"/>
+      <c r="G1" s="101" t="s">
         <v>85</v>
       </c>
-      <c r="H1" s="89"/>
-      <c r="I1" s="89"/>
-      <c r="J1" s="89"/>
-      <c r="M1" s="95" t="s">
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="M1" s="94" t="s">
         <v>89</v>
       </c>
-      <c r="N1" s="95"/>
-      <c r="O1" s="95"/>
-      <c r="P1" s="95"/>
-      <c r="Q1" s="95"/>
-    </row>
-    <row r="2" spans="1:17" ht="18">
-      <c r="A2" s="35" t="s">
+      <c r="N1" s="94"/>
+      <c r="O1" s="94"/>
+      <c r="P1" s="94"/>
+    </row>
+    <row r="2" spans="1:16" ht="18">
+      <c r="A2" s="98" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="37"/>
-      <c r="G2" s="90" t="s">
+      <c r="B2" s="99"/>
+      <c r="C2" s="99"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="100"/>
+      <c r="G2" s="102" t="s">
         <v>70</v>
       </c>
-      <c r="H2" s="90"/>
-      <c r="I2" s="90"/>
-      <c r="J2" s="90"/>
-    </row>
-    <row r="3" spans="1:17" ht="18">
+      <c r="H2" s="102"/>
+      <c r="I2" s="102"/>
+      <c r="J2" s="102"/>
+      <c r="M2" s="82" t="s">
+        <v>118</v>
+      </c>
+      <c r="N2" s="80" t="s">
+        <v>90</v>
+      </c>
+      <c r="O2" s="80" t="s">
+        <v>91</v>
+      </c>
+      <c r="P2" s="80" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="18">
       <c r="A3" s="16" t="s">
         <v>12</v>
       </c>
@@ -1810,14 +2293,24 @@
       <c r="C3" s="10"/>
       <c r="D3" s="10"/>
       <c r="E3" s="15"/>
-      <c r="G3" s="91" t="s">
+      <c r="G3" s="93" t="s">
         <v>86</v>
       </c>
-      <c r="H3" s="91"/>
-      <c r="I3" s="91"/>
-      <c r="J3" s="91"/>
-    </row>
-    <row r="4" spans="1:17" s="4" customFormat="1" ht="18">
+      <c r="H3" s="93"/>
+      <c r="I3" s="93"/>
+      <c r="J3" s="93"/>
+      <c r="M3" s="63" t="s">
+        <v>93</v>
+      </c>
+      <c r="N3" s="63">
+        <v>10</v>
+      </c>
+      <c r="O3" s="76"/>
+      <c r="P3" s="63" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="4" customFormat="1" ht="18">
       <c r="A4" s="17" t="s">
         <v>0</v>
       </c>
@@ -1833,35 +2326,30 @@
       <c r="E4" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="88" t="s">
+      <c r="G4" s="72" t="s">
         <v>36</v>
       </c>
-      <c r="H4" s="88" t="s">
+      <c r="H4" s="72" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="88" t="s">
+      <c r="I4" s="72" t="s">
         <v>76</v>
       </c>
-      <c r="J4" s="63" t="s">
+      <c r="J4" s="51" t="s">
         <v>77</v>
       </c>
-      <c r="M4" s="66" t="s">
-        <v>36</v>
-      </c>
-      <c r="N4" s="66" t="s">
-        <v>90</v>
-      </c>
-      <c r="O4" s="66" t="s">
-        <v>102</v>
-      </c>
-      <c r="P4" s="66" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q4" s="66" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="15.6">
+      <c r="M4" s="63" t="s">
+        <v>94</v>
+      </c>
+      <c r="N4" s="63">
+        <v>20</v>
+      </c>
+      <c r="O4" s="63"/>
+      <c r="P4" s="63" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="15.6">
       <c r="A5" s="18">
         <v>1</v>
       </c>
@@ -1877,31 +2365,33 @@
       <c r="E5" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="86" t="s">
+      <c r="G5" s="70" t="s">
         <v>71</v>
       </c>
-      <c r="H5" s="86" t="s">
+      <c r="H5" s="70" t="s">
         <v>59</v>
       </c>
-      <c r="I5" s="86" t="s">
+      <c r="I5" s="70" t="s">
         <v>87</v>
       </c>
-      <c r="J5" s="86" t="s">
+      <c r="J5" s="70" t="s">
         <v>81</v>
       </c>
-      <c r="M5" s="86" t="s">
-        <v>93</v>
-      </c>
-      <c r="N5" s="77">
-        <v>10</v>
-      </c>
-      <c r="O5" s="77"/>
-      <c r="P5" s="77"/>
-      <c r="Q5" s="77" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="15.6">
+      <c r="M5" s="83" t="s">
+        <v>95</v>
+      </c>
+      <c r="N5" s="55">
+        <f>N3+N4</f>
+        <v>30</v>
+      </c>
+      <c r="O5" s="55" t="s">
+        <v>97</v>
+      </c>
+      <c r="P5" s="55" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="15.6">
       <c r="A6" s="18">
         <v>2</v>
       </c>
@@ -1917,31 +2407,33 @@
       <c r="E6" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="G6" s="86" t="s">
+      <c r="G6" s="70" t="s">
         <v>72</v>
       </c>
-      <c r="H6" s="86" t="s">
+      <c r="H6" s="70" t="s">
         <v>78</v>
       </c>
-      <c r="I6" s="86">
+      <c r="I6" s="70">
         <v>123</v>
       </c>
-      <c r="J6" s="86" t="s">
+      <c r="J6" s="70" t="s">
         <v>82</v>
       </c>
-      <c r="M6" s="77" t="s">
-        <v>94</v>
-      </c>
-      <c r="N6" s="77">
-        <v>20</v>
-      </c>
-      <c r="O6" s="77"/>
-      <c r="P6" s="77"/>
-      <c r="Q6" s="77" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" ht="15.6">
+      <c r="M6" s="61" t="s">
+        <v>96</v>
+      </c>
+      <c r="N6" s="61">
+        <f>$N$3+$N$4</f>
+        <v>30</v>
+      </c>
+      <c r="O6" s="61" t="s">
+        <v>98</v>
+      </c>
+      <c r="P6" s="84" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="15.6">
       <c r="A7" s="18">
         <v>3</v>
       </c>
@@ -1957,87 +2449,64 @@
       <c r="E7" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="86" t="s">
+      <c r="G7" s="70" t="s">
         <v>73</v>
       </c>
-      <c r="H7" s="86" t="s">
+      <c r="H7" s="70" t="s">
         <v>79</v>
       </c>
-      <c r="I7" s="92">
+      <c r="I7" s="73">
         <v>45876</v>
       </c>
-      <c r="J7" s="86" t="s">
+      <c r="J7" s="70" t="s">
         <v>83</v>
       </c>
-      <c r="M7" s="77" t="s">
-        <v>95</v>
-      </c>
-      <c r="N7" s="77" t="e">
-        <f>M1+M2</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O7" s="77"/>
-      <c r="P7" s="77" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q7" s="77" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" ht="15.6">
+      <c r="M7" s="63"/>
+      <c r="N7" s="63"/>
+      <c r="O7" s="63"/>
+      <c r="P7" s="63"/>
+    </row>
+    <row r="8" spans="1:16" ht="15.6">
       <c r="A8" s="18"/>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
       <c r="D8" s="10"/>
       <c r="E8" s="15"/>
-      <c r="G8" s="86" t="s">
+      <c r="G8" s="70" t="s">
         <v>74</v>
       </c>
-      <c r="H8" s="86" t="s">
+      <c r="H8" s="70" t="s">
         <v>80</v>
       </c>
-      <c r="I8" s="86" t="s">
+      <c r="I8" s="70" t="s">
         <v>88</v>
       </c>
-      <c r="J8" s="86" t="s">
+      <c r="J8" s="70" t="s">
         <v>84</v>
       </c>
-      <c r="M8" s="86" t="s">
-        <v>96</v>
-      </c>
-      <c r="N8" s="77" t="e">
-        <f>$M$1+$M$2</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O8" s="77"/>
-      <c r="P8" s="77" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q8" s="93" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17">
+      <c r="M8" s="70"/>
+      <c r="N8" s="63"/>
+      <c r="O8" s="63"/>
+      <c r="P8" s="74"/>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9" s="18"/>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
       <c r="D9" s="10"/>
       <c r="E9" s="15"/>
     </row>
-    <row r="10" spans="1:17" ht="15" thickBot="1">
+    <row r="10" spans="1:16" ht="15" thickBot="1">
       <c r="A10" s="19"/>
       <c r="B10" s="20"/>
       <c r="C10" s="20"/>
       <c r="D10" s="20"/>
       <c r="E10" s="21"/>
     </row>
-    <row r="15" spans="1:17">
-      <c r="O15" s="94"/>
-    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="G3:J3"/>
-    <mergeCell ref="M1:Q1"/>
+    <mergeCell ref="M1:P1"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="G1:J1"/>
@@ -2045,4 +2514,394 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6E05485-FFCE-462B-89FD-A4525077A365}">
+  <dimension ref="A1:J20"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="4" width="15.77734375" customWidth="1"/>
+    <col min="9" max="9" width="16.5546875" customWidth="1"/>
+    <col min="10" max="10" width="100" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="23.4">
+      <c r="A1" s="103" t="s">
+        <v>100</v>
+      </c>
+      <c r="B1" s="103"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="103"/>
+      <c r="I1" s="106" t="s">
+        <v>124</v>
+      </c>
+      <c r="J1" s="106"/>
+    </row>
+    <row r="2" spans="1:10" ht="18">
+      <c r="A2" s="104" t="s">
+        <v>101</v>
+      </c>
+      <c r="B2" s="104"/>
+      <c r="C2" s="104"/>
+      <c r="D2" s="104"/>
+      <c r="I2" s="107" t="s">
+        <v>125</v>
+      </c>
+      <c r="J2" s="107"/>
+    </row>
+    <row r="3" spans="1:10" ht="18">
+      <c r="A3" s="77" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="79"/>
+      <c r="I3" s="107" t="s">
+        <v>126</v>
+      </c>
+      <c r="J3" s="107"/>
+    </row>
+    <row r="4" spans="1:10" ht="21">
+      <c r="A4" s="77" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="79"/>
+      <c r="I4" s="108" t="s">
+        <v>121</v>
+      </c>
+      <c r="J4" s="109" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="19.95" customHeight="1">
+      <c r="A5" s="81" t="s">
+        <v>105</v>
+      </c>
+      <c r="B5" s="80" t="s">
+        <v>103</v>
+      </c>
+      <c r="C5" s="80" t="s">
+        <v>115</v>
+      </c>
+      <c r="D5" s="80" t="s">
+        <v>116</v>
+      </c>
+      <c r="I5" s="111" t="s">
+        <v>122</v>
+      </c>
+      <c r="J5" s="110" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="19.95" customHeight="1">
+      <c r="A6" s="112" t="s">
+        <v>110</v>
+      </c>
+      <c r="B6" s="113">
+        <v>45</v>
+      </c>
+      <c r="C6" s="114">
+        <f>SUM(B6:B10)</f>
+        <v>230</v>
+      </c>
+      <c r="D6" s="115" t="s">
+        <v>107</v>
+      </c>
+      <c r="I6" s="111" t="s">
+        <v>123</v>
+      </c>
+      <c r="J6" s="110" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="19.95" customHeight="1">
+      <c r="A7" s="112" t="s">
+        <v>111</v>
+      </c>
+      <c r="B7" s="113">
+        <v>50</v>
+      </c>
+      <c r="C7" s="114">
+        <f>AVERAGE(B6:B10)</f>
+        <v>46</v>
+      </c>
+      <c r="D7" s="115" t="s">
+        <v>106</v>
+      </c>
+      <c r="I7" s="111" t="s">
+        <v>127</v>
+      </c>
+      <c r="J7" s="110" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="19.95" customHeight="1">
+      <c r="A8" s="112" t="s">
+        <v>112</v>
+      </c>
+      <c r="B8" s="113">
+        <v>60</v>
+      </c>
+      <c r="C8" s="114">
+        <f>MAX(B6:B10)</f>
+        <v>60</v>
+      </c>
+      <c r="D8" s="115" t="s">
+        <v>108</v>
+      </c>
+      <c r="I8" s="111" t="s">
+        <v>128</v>
+      </c>
+      <c r="J8" s="110" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="19.95" customHeight="1">
+      <c r="A9" s="112" t="s">
+        <v>113</v>
+      </c>
+      <c r="B9" s="113">
+        <v>40</v>
+      </c>
+      <c r="C9" s="114">
+        <f>MIN(B6:B10)</f>
+        <v>35</v>
+      </c>
+      <c r="D9" s="115" t="s">
+        <v>109</v>
+      </c>
+      <c r="I9" s="111" t="s">
+        <v>129</v>
+      </c>
+      <c r="J9" s="110" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="19.95" customHeight="1">
+      <c r="A10" s="112" t="s">
+        <v>114</v>
+      </c>
+      <c r="B10" s="113">
+        <v>35</v>
+      </c>
+      <c r="C10" s="114" t="str">
+        <f>IF(B6&gt;40,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="D10" s="115" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="105"/>
+      <c r="B20" s="105"/>
+      <c r="C20" s="105"/>
+      <c r="D20" s="105"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="I1:J1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF293D10-98AC-44ED-A555-FC2B549B565A}">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="18.44140625" customWidth="1"/>
+    <col min="2" max="2" width="11.88671875" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.6640625" customWidth="1"/>
+    <col min="6" max="6" width="19.6640625" customWidth="1"/>
+    <col min="7" max="7" width="26" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="21">
+      <c r="A1" s="118" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1" s="118"/>
+      <c r="C1" s="118"/>
+      <c r="D1" s="118"/>
+      <c r="E1" s="118"/>
+      <c r="F1" s="118"/>
+    </row>
+    <row r="2" spans="1:6" ht="15.6">
+      <c r="A2" s="120" t="s">
+        <v>136</v>
+      </c>
+      <c r="B2" s="120"/>
+      <c r="C2" s="120"/>
+      <c r="D2" s="120"/>
+      <c r="E2" s="120"/>
+      <c r="F2" s="121"/>
+    </row>
+    <row r="3" spans="1:6" ht="15.6">
+      <c r="A3" s="122" t="s">
+        <v>137</v>
+      </c>
+      <c r="B3" s="122"/>
+      <c r="C3" s="122"/>
+      <c r="D3" s="122"/>
+      <c r="E3" s="122"/>
+      <c r="F3" s="123"/>
+    </row>
+    <row r="4" spans="1:6" ht="15.6">
+      <c r="A4" s="117" t="s">
+        <v>138</v>
+      </c>
+      <c r="B4" s="117"/>
+      <c r="C4" s="117"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="124"/>
+    </row>
+    <row r="5" spans="1:6" ht="18">
+      <c r="A5" s="119" t="s">
+        <v>139</v>
+      </c>
+      <c r="B5" s="119" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="119" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="119" t="s">
+        <v>141</v>
+      </c>
+      <c r="E5" s="119" t="s">
+        <v>140</v>
+      </c>
+      <c r="F5" s="119" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15.6">
+      <c r="A6" s="110" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="116">
+        <v>80</v>
+      </c>
+      <c r="C6" s="116">
+        <v>90</v>
+      </c>
+      <c r="D6" s="128">
+        <f>B6+C6</f>
+        <v>170</v>
+      </c>
+      <c r="E6" s="129">
+        <f>(B6+C6)/2</f>
+        <v>85</v>
+      </c>
+      <c r="F6" s="113" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15.6">
+      <c r="A7" s="110" t="s">
+        <v>142</v>
+      </c>
+      <c r="B7" s="116">
+        <v>85</v>
+      </c>
+      <c r="C7" s="116">
+        <v>95</v>
+      </c>
+      <c r="D7" s="128">
+        <f t="shared" ref="D7:D9" si="0">B7+C7</f>
+        <v>180</v>
+      </c>
+      <c r="E7" s="129">
+        <f t="shared" ref="E7:E9" si="1">(B7+C7)/2</f>
+        <v>90</v>
+      </c>
+      <c r="F7" s="113" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15.6">
+      <c r="A8" s="110" t="s">
+        <v>143</v>
+      </c>
+      <c r="B8" s="116">
+        <v>78</v>
+      </c>
+      <c r="C8" s="116">
+        <v>88</v>
+      </c>
+      <c r="D8" s="128">
+        <f t="shared" si="0"/>
+        <v>166</v>
+      </c>
+      <c r="E8" s="129">
+        <f t="shared" si="1"/>
+        <v>83</v>
+      </c>
+      <c r="F8" s="113" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15.6">
+      <c r="A9" s="110" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="116">
+        <v>92</v>
+      </c>
+      <c r="C9" s="116">
+        <v>85</v>
+      </c>
+      <c r="D9" s="128">
+        <f t="shared" si="0"/>
+        <v>177</v>
+      </c>
+      <c r="E9" s="129">
+        <f t="shared" si="1"/>
+        <v>88.5</v>
+      </c>
+      <c r="F9" s="113" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15.6">
+      <c r="A10" s="125" t="s">
+        <v>144</v>
+      </c>
+      <c r="B10" s="126">
+        <f>AVERAGE($B$6:$B$9)</f>
+        <v>83.75</v>
+      </c>
+      <c r="C10" s="126">
+        <f>AVERAGE($C$6:$C$9)</f>
+        <v>89.5</v>
+      </c>
+      <c r="D10" s="126">
+        <f>$B$10+$C$10</f>
+        <v>173.25</v>
+      </c>
+      <c r="E10" s="126">
+        <f>($B$10+$C$10)/2</f>
+        <v>86.625</v>
+      </c>
+      <c r="F10" s="127" t="s">
+        <v>147</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>